--- a/北部山头3970平台2026/7、单日数据/北部山头3970平台-1011/3970平台 1011炮孔数据报告.xlsx
+++ b/北部山头3970平台2026/7、单日数据/北部山头3970平台-1011/3970平台 1011炮孔数据报告.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AAAWK\2026地质生产数据\北部山头2026\北部山头3970平台2026\7、单日数据\北部山头3970平台-1011\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WK\N CRT\北部山头3970平台2026\7、单日数据\北部山头3970平台-1011\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1D4836-BC98-4A55-BB5E-95B9588038C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="20556" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="1104" windowWidth="23016" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="181" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -189,7 +189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -211,6 +211,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -220,55 +253,10 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -553,19 +541,19 @@
   <sheetFormatPr defaultColWidth="18.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18.5546875" style="2"/>
-    <col min="5" max="5" width="18.5546875" style="21"/>
+    <col min="5" max="5" width="18.5546875" style="12"/>
     <col min="6" max="16384" width="18.5546875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -580,7 +568,7 @@
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="10" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -600,7 +588,7 @@
       <c r="D3" s="4">
         <v>989.32</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="11">
         <v>1.139</v>
       </c>
       <c r="F3" s="4">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="4"/>
@@ -620,7 +608,7 @@
         <f t="shared" ref="D4:F4" si="0">D3</f>
         <v>989.32</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="11">
         <f t="shared" si="0"/>
         <v>1.139</v>
       </c>
@@ -642,7 +630,7 @@
       <c r="D5" s="4">
         <v>22806.733</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="11">
         <v>0.64700000000000002</v>
       </c>
       <c r="F5" s="4">
@@ -650,7 +638,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1">
@@ -662,7 +650,7 @@
       <c r="D6" s="1">
         <v>739.61199999999997</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="10">
         <v>0.8</v>
       </c>
       <c r="F6" s="1">
@@ -682,7 +670,7 @@
         <f t="shared" ref="D7:F7" si="1">D5+D6</f>
         <v>23546.345000000001</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="11">
         <f>F7/D7*100</f>
         <v>0.65143868400807003</v>
       </c>
@@ -704,7 +692,7 @@
         <f>D4+D7</f>
         <v>24535.665000000001</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="11">
         <f>F8/D8*100</f>
         <v>0.67108431746194785</v>
       </c>
@@ -718,7 +706,7 @@
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
-      <c r="E9" s="22"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -726,7 +714,7 @@
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="23"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -734,7 +722,7 @@
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="E11" s="22"/>
+      <c r="E11" s="13"/>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -742,7 +730,7 @@
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
-      <c r="E12" s="23"/>
+      <c r="E12" s="14"/>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -750,97 +738,97 @@
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="22"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="8">
         <v>1</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>366.41500000000002</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="8">
         <v>989.32</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="15">
         <v>1.139</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="8">
         <v>11.265000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11">
+      <c r="B17" s="7"/>
+      <c r="C17" s="8">
         <v>366.41500000000002</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="8">
         <v>989.32</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="15">
         <v>1.139</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="8">
         <v>11.265000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11">
+      <c r="B18" s="7"/>
+      <c r="C18" s="8">
         <v>366.41500000000002</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="8">
         <v>989.32</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="15">
         <v>1.139</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="8">
         <v>11.265000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="3">
@@ -854,7 +842,7 @@
         <f t="shared" ref="D19:F19" si="2">D18</f>
         <v>989.32</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="16">
         <f t="shared" si="2"/>
         <v>1.139</v>
       </c>
@@ -868,155 +856,155 @@
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="25"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="8">
         <v>1</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="8">
         <v>434.09100000000001</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="8">
         <v>1172.047</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="15">
         <v>1.1100000000000001</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="8">
         <v>13.01</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="16">
+      <c r="B24" s="7"/>
+      <c r="C24" s="8">
         <v>434.09100000000001</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="8">
         <v>1172.047</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="15">
         <v>1.1100000000000001</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="8">
         <v>13.01</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="8">
         <v>2</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="8">
         <v>1524.394</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="8">
         <v>4115.8649999999998</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="15">
         <v>0.61899999999999999</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="8">
         <v>25.466000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="8">
         <v>3</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="8">
         <v>6488.4520000000002</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="8">
         <v>17518.822</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="15">
         <v>0.622</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="8">
         <v>108.998</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="16">
+      <c r="B27" s="7"/>
+      <c r="C27" s="8">
         <v>8012.8469999999998</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="8">
         <v>21634.686000000002</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="15">
         <v>0.622</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="8">
         <v>134.46299999999999</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16">
+      <c r="B28" s="7"/>
+      <c r="C28" s="8">
         <v>8446.9380000000001</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="8">
         <v>22806.733</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="15">
         <v>0.64700000000000002</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="8">
         <v>147.47300000000001</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2">
@@ -1030,7 +1018,7 @@
         <f t="shared" ref="D29:F29" si="3">D28</f>
         <v>22806.733</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="12">
         <f t="shared" si="3"/>
         <v>0.64700000000000002</v>
       </c>
@@ -1040,93 +1028,93 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="8">
         <v>1</v>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="8">
         <v>273.93099999999998</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="8">
         <v>739.61199999999997</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="15">
         <v>0.8</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="8">
         <v>5.9169999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="18">
+      <c r="B34" s="7"/>
+      <c r="C34" s="8">
         <v>273.93099999999998</v>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="8">
         <v>739.61199999999997</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="15">
         <v>0.8</v>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="8">
         <v>5.9169999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="18">
+      <c r="B35" s="7"/>
+      <c r="C35" s="8">
         <v>273.93099999999998</v>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="8">
         <v>739.61199999999997</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="15">
         <v>0.8</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="8">
         <v>5.9169999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2">
@@ -1140,7 +1128,7 @@
         <f t="shared" ref="D36:F36" si="4">D35</f>
         <v>739.61199999999997</v>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="12">
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
